--- a/var_results/all_runs.xlsx
+++ b/var_results/all_runs.xlsx
@@ -1,37 +1,110 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varce\OneDrive\Escritorio\codigos\ATO_PRICING\var_results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3ADAD8-0AA3-4A08-909B-A71B23BED845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="20098" windowHeight="10671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>seed</t>
+  </si>
+  <si>
+    <t>incumbent</t>
+  </si>
+  <si>
+    <t>bestbd</t>
+  </si>
+  <si>
+    <t>gap</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>Fill Rate</t>
+  </si>
+  <si>
+    <t>Utilization Rate</t>
+  </si>
+  <si>
+    <t>Inventory Service Rate</t>
+  </si>
+  <si>
+    <t>Weighted Avg Price</t>
+  </si>
+  <si>
+    <t>MS_linear</t>
+  </si>
+  <si>
+    <t>AF_EVAL</t>
+  </si>
+  <si>
+    <t>REL_EVAL</t>
+  </si>
+  <si>
+    <t>IH</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +119,51 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,218 +451,214 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="5"/>
+    <col min="6" max="6" width="8.7265625" style="5"/>
+    <col min="7" max="7" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.453125" style="5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>incumbent</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>bestbd</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>gap</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>iterations (IH)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>vss</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>evpi</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>vss_ts</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Fill Rate</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Utilization Rate</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Inventory Service Rate</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Weighted Avg Price</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AF_EVAL</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
-        <v>2299.656279564313</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2" s="5">
+        <v>2478.8000845042188</v>
+      </c>
+      <c r="D2" s="5">
+        <v>2478.8000845042188</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.50300002098083496</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.6823242608833533</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.23897684506312039</v>
+      </c>
+      <c r="J2" s="5">
+        <v>52.474838597859367</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5">
+        <v>2299.6562795643131</v>
+      </c>
+      <c r="D3" s="5">
         <v>2299.656279564334</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>3.528000116348267</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.7809550134069613</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="E3" s="3">
+        <f>($C$2-C3)/$C$2</f>
+        <v>7.2270372290121995E-2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>3.279999732971191</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.78095501340696127</v>
+      </c>
+      <c r="H3" s="3">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0.2642088639693428</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="I3" s="3">
+        <v>0.26420886396934279</v>
+      </c>
+      <c r="J3" s="5">
         <v>52.12526866113587</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REL_EVAL</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C3" t="n">
-        <v>2433.840980271387</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C4" s="5">
+        <v>2433.8409802713868</v>
+      </c>
+      <c r="D4" s="5">
         <v>2433.8409802714</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.6239998340606689</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.6704648331694882</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="E4" s="3">
+        <f t="shared" ref="E4:E6" si="0">($C$2-C4)/$C$2</f>
+        <v>1.8137446627457348E-2</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.4309999942779541</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.67046483316948824</v>
+      </c>
+      <c r="H4" s="3">
         <v>1</v>
       </c>
-      <c r="M3" t="n">
-        <v>0.2464805696838807</v>
-      </c>
-      <c r="N3" t="n">
-        <v>52.4258147677544</v>
+      <c r="I4" s="3">
+        <v>0.24648056968388071</v>
+      </c>
+      <c r="J4" s="5">
+        <v>52.425814767754403</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>IH</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
-        <v>1393.487305192307</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1393.487305192307</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3.885009527206421</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="C5" s="5">
+        <v>1557.752131379995</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1557.9061630526739</v>
+      </c>
+      <c r="E5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.37157008299378091</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3.074151992797852</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.30284942379632601</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.99872418402677465</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0.28625799886427178</v>
+      </c>
+      <c r="J5" s="5">
+        <v>57.480231763701887</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5">
+        <v>2439.8151679024108</v>
+      </c>
+      <c r="D6" s="5">
+        <v>2440.0538413675472</v>
+      </c>
+      <c r="E6" s="3">
+        <f t="shared" si="0"/>
+        <v>1.5727333900589769E-2</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.37700009346008301</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.69107400694141541</v>
+      </c>
+      <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2433380137966747</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.9983170356272283</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.3168197461262501</v>
-      </c>
-      <c r="N4" t="n">
-        <v>60.00000000000001</v>
+      <c r="I6" s="3">
+        <v>0.24982453568027879</v>
+      </c>
+      <c r="J6" s="5">
+        <v>52.563154338072167</v>
       </c>
     </row>
   </sheetData>

--- a/var_results/all_runs.xlsx
+++ b/var_results/all_runs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varce\OneDrive\Escritorio\codigos\ATO_PRICING\var_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA3ADAD8-0AA3-4A08-909B-A71B23BED845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966AA2A6-6691-4517-B129-3242BC0BEC0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="20098" windowHeight="10671" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="21">
   <si>
     <t>Model</t>
   </si>
@@ -51,6 +51,18 @@
   </si>
   <si>
     <t>time</t>
+  </si>
+  <si>
+    <t>iterations (IH)</t>
+  </si>
+  <si>
+    <t>vss</t>
+  </si>
+  <si>
+    <t>evpi</t>
+  </si>
+  <si>
+    <t>vss_ts</t>
   </si>
   <si>
     <t>Fill Rate</t>
@@ -77,16 +89,19 @@
     <t>IH</t>
   </si>
   <si>
-    <t>-</t>
+    <t>REL_EVAL_LS</t>
+  </si>
+  <si>
+    <t>IH_LS</t>
+  </si>
+  <si>
+    <t>AF_EVAL_LS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -137,19 +152,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,213 +459,4449 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="4.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="5"/>
-    <col min="6" max="6" width="8.7265625" style="5"/>
-    <col min="7" max="7" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.90625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B2">
         <v>5</v>
       </c>
-      <c r="C2" s="5">
-        <v>2478.8000845042188</v>
-      </c>
-      <c r="D2" s="5">
-        <v>2478.8000845042188</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="C2">
+        <v>2178.901964320868</v>
+      </c>
+      <c r="D2">
+        <v>2178.901964320868</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1.471999883651733</v>
+      </c>
+      <c r="H2">
+        <v>-1</v>
+      </c>
+      <c r="I2">
+        <v>-1</v>
+      </c>
+      <c r="J2">
+        <v>-1</v>
+      </c>
+      <c r="K2">
+        <v>0.22908482502029659</v>
+      </c>
+      <c r="L2">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="M2">
+        <v>0.25369007016746048</v>
+      </c>
+      <c r="N2">
+        <v>56.200217637801892</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="5">
-        <v>0.50300002098083496</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.6823242608833533</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0.23897684506312039</v>
-      </c>
-      <c r="J2" s="5">
-        <v>52.474838597859367</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>2125.2943004545868</v>
+      </c>
+      <c r="D3">
+        <v>2125.2943004545868</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1.5550000667572019</v>
+      </c>
+      <c r="H3">
+        <v>-1</v>
+      </c>
+      <c r="I3">
+        <v>-1</v>
+      </c>
+      <c r="J3">
+        <v>-1</v>
+      </c>
+      <c r="K3">
+        <v>0.23488865600258679</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0.2178484232505882</v>
+      </c>
+      <c r="N3">
+        <v>56.35162928323038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>2165.3488998869698</v>
+      </c>
+      <c r="D4">
+        <v>2165.3488998869698</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1.7309999465942381</v>
+      </c>
+      <c r="H4">
+        <v>-1</v>
+      </c>
+      <c r="I4">
+        <v>-1</v>
+      </c>
+      <c r="J4">
+        <v>-1</v>
+      </c>
+      <c r="K4">
+        <v>0.32103311579197857</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>0.25660906880097278</v>
+      </c>
+      <c r="N4">
+        <v>55.874358208308969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>2009.635756124464</v>
+      </c>
+      <c r="D5">
+        <v>2009.635756124464</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1.3119997978210449</v>
+      </c>
+      <c r="H5">
+        <v>-1</v>
+      </c>
+      <c r="I5">
+        <v>-1</v>
+      </c>
+      <c r="J5">
+        <v>-1</v>
+      </c>
+      <c r="K5">
+        <v>0.4948200494223543</v>
+      </c>
+      <c r="L5">
+        <v>0.99985339365225989</v>
+      </c>
+      <c r="M5">
+        <v>0.28513819813888741</v>
+      </c>
+      <c r="N5">
+        <v>56.05630000341732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>2087.8786118983612</v>
+      </c>
+      <c r="D6">
+        <v>2087.8786118983612</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>1.220000028610229</v>
+      </c>
+      <c r="H6">
+        <v>-1</v>
+      </c>
+      <c r="I6">
+        <v>-1</v>
+      </c>
+      <c r="J6">
+        <v>-1</v>
+      </c>
+      <c r="K6">
+        <v>0.19949825479627781</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>0.24789636592110789</v>
+      </c>
+      <c r="N6">
+        <v>55.476572727433187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>2173.5222498371609</v>
+      </c>
+      <c r="D7">
+        <v>2173.5222498371609</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1.25</v>
+      </c>
+      <c r="H7">
+        <v>-1</v>
+      </c>
+      <c r="I7">
+        <v>-1</v>
+      </c>
+      <c r="J7">
+        <v>-1</v>
+      </c>
+      <c r="K7">
+        <v>0.27481272359477937</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>0.2481073129618484</v>
+      </c>
+      <c r="N7">
+        <v>56.217667687993348</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
         <v>11</v>
       </c>
-      <c r="B3">
+      <c r="C8">
+        <v>2113.529828285948</v>
+      </c>
+      <c r="D8">
+        <v>2113.529828285948</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>1.299000024795532</v>
+      </c>
+      <c r="H8">
+        <v>-1</v>
+      </c>
+      <c r="I8">
+        <v>-1</v>
+      </c>
+      <c r="J8">
+        <v>-1</v>
+      </c>
+      <c r="K8">
+        <v>0.22406674781864</v>
+      </c>
+      <c r="L8">
+        <v>0.99975699087013614</v>
+      </c>
+      <c r="M8">
+        <v>0.25292207098834829</v>
+      </c>
+      <c r="N8">
+        <v>56.142734131644737</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>12</v>
+      </c>
+      <c r="C9">
+        <v>2163.2140703527298</v>
+      </c>
+      <c r="D9">
+        <v>2163.2140703527298</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1.361999988555908</v>
+      </c>
+      <c r="H9">
+        <v>-1</v>
+      </c>
+      <c r="I9">
+        <v>-1</v>
+      </c>
+      <c r="J9">
+        <v>-1</v>
+      </c>
+      <c r="K9">
+        <v>0.22380346785520869</v>
+      </c>
+      <c r="L9">
+        <v>0.99956378711980942</v>
+      </c>
+      <c r="M9">
+        <v>0.19905630378798489</v>
+      </c>
+      <c r="N9">
+        <v>56.13692768803741</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>13</v>
+      </c>
+      <c r="C10">
+        <v>2130.1202308147972</v>
+      </c>
+      <c r="D10">
+        <v>2130.1202308147972</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1.5480000972747801</v>
+      </c>
+      <c r="H10">
+        <v>-1</v>
+      </c>
+      <c r="I10">
+        <v>-1</v>
+      </c>
+      <c r="J10">
+        <v>-1</v>
+      </c>
+      <c r="K10">
+        <v>0.26054554873220648</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10">
+        <v>0.23995873402235501</v>
+      </c>
+      <c r="N10">
+        <v>56.079217809537511</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <v>14</v>
+      </c>
+      <c r="C11">
+        <v>2052.103427429337</v>
+      </c>
+      <c r="D11">
+        <v>2052.103427429337</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1.401999950408936</v>
+      </c>
+      <c r="H11">
+        <v>-1</v>
+      </c>
+      <c r="I11">
+        <v>-1</v>
+      </c>
+      <c r="J11">
+        <v>-1</v>
+      </c>
+      <c r="K11">
+        <v>0.22493593184488689</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>0.26860022157685048</v>
+      </c>
+      <c r="N11">
+        <v>56.205143701353563</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>2328.2373802564171</v>
+      </c>
+      <c r="D12">
+        <v>2328.2373802564171</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1.3670001029968259</v>
+      </c>
+      <c r="H12">
+        <v>-1</v>
+      </c>
+      <c r="I12">
+        <v>-1</v>
+      </c>
+      <c r="J12">
+        <v>-1</v>
+      </c>
+      <c r="K12">
+        <v>0.67176715970943901</v>
+      </c>
+      <c r="L12">
+        <v>0.9999436672968417</v>
+      </c>
+      <c r="M12">
+        <v>0.2226719881655688</v>
+      </c>
+      <c r="N12">
+        <v>56.262849785598007</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13">
+        <v>16</v>
+      </c>
+      <c r="C13">
+        <v>2185.6498371692869</v>
+      </c>
+      <c r="D13">
+        <v>2185.6498371692869</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1.281999826431274</v>
+      </c>
+      <c r="H13">
+        <v>-1</v>
+      </c>
+      <c r="I13">
+        <v>-1</v>
+      </c>
+      <c r="J13">
+        <v>-1</v>
+      </c>
+      <c r="K13">
+        <v>0.26986328883115079</v>
+      </c>
+      <c r="L13">
+        <v>0.99982061086636309</v>
+      </c>
+      <c r="M13">
+        <v>0.1962058068461347</v>
+      </c>
+      <c r="N13">
+        <v>56.320790502257331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>2201.2443445940689</v>
+      </c>
+      <c r="D14">
+        <v>2201.2443445940689</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="H14">
+        <v>-1</v>
+      </c>
+      <c r="I14">
+        <v>-1</v>
+      </c>
+      <c r="J14">
+        <v>-1</v>
+      </c>
+      <c r="K14">
+        <v>0.28646816958915899</v>
+      </c>
+      <c r="L14">
+        <v>0.99999999999999978</v>
+      </c>
+      <c r="M14">
+        <v>0.24247176682998009</v>
+      </c>
+      <c r="N14">
+        <v>56.294122625425572</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>18</v>
+      </c>
+      <c r="C15">
+        <v>2209.5635601435451</v>
+      </c>
+      <c r="D15">
+        <v>2209.5635601435451</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>1.1819999217987061</v>
+      </c>
+      <c r="H15">
+        <v>-1</v>
+      </c>
+      <c r="I15">
+        <v>-1</v>
+      </c>
+      <c r="J15">
+        <v>-1</v>
+      </c>
+      <c r="K15">
+        <v>0.31610437607967129</v>
+      </c>
+      <c r="L15">
+        <v>0.99990977708932749</v>
+      </c>
+      <c r="M15">
+        <v>0.2589012048983399</v>
+      </c>
+      <c r="N15">
+        <v>56.1105548846311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+      <c r="C16">
+        <v>2020.8114535689281</v>
+      </c>
+      <c r="D16">
+        <v>2020.8114535689281</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>1.1700000762939451</v>
+      </c>
+      <c r="H16">
+        <v>-1</v>
+      </c>
+      <c r="I16">
+        <v>-1</v>
+      </c>
+      <c r="J16">
+        <v>-1</v>
+      </c>
+      <c r="K16">
+        <v>0.22370346815349179</v>
+      </c>
+      <c r="L16">
+        <v>0.99982339107128637</v>
+      </c>
+      <c r="M16">
+        <v>0.26198480839207738</v>
+      </c>
+      <c r="N16">
+        <v>56.285875093624959</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
         <v>5</v>
       </c>
-      <c r="C3" s="5">
-        <v>2299.6562795643131</v>
-      </c>
-      <c r="D3" s="5">
-        <v>2299.656279564334</v>
-      </c>
-      <c r="E3" s="3">
-        <f>($C$2-C3)/$C$2</f>
-        <v>7.2270372290121995E-2</v>
-      </c>
-      <c r="F3" s="5">
-        <v>3.279999732971191</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.78095501340696127</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0.26420886396934279</v>
-      </c>
-      <c r="J3" s="5">
-        <v>52.12526866113587</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="C17">
+        <v>2102.2820129772808</v>
+      </c>
+      <c r="D17">
+        <v>2102.2820129772808</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>8.7820000648498535</v>
+      </c>
+      <c r="H17">
+        <v>-1</v>
+      </c>
+      <c r="I17">
+        <v>-1</v>
+      </c>
+      <c r="J17">
+        <v>-1</v>
+      </c>
+      <c r="K17">
+        <v>0.33756588672083759</v>
+      </c>
+      <c r="L17">
+        <v>0.99975410488222682</v>
+      </c>
+      <c r="M17">
+        <v>0.28779955771296167</v>
+      </c>
+      <c r="N17">
+        <v>56.44582031172623</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>6</v>
+      </c>
+      <c r="C18">
+        <v>2060.1687731333809</v>
+      </c>
+      <c r="D18">
+        <v>2060.16877313339</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>8.437999963760376</v>
+      </c>
+      <c r="H18">
+        <v>-1</v>
+      </c>
+      <c r="I18">
+        <v>-1</v>
+      </c>
+      <c r="J18">
+        <v>-1</v>
+      </c>
+      <c r="K18">
+        <v>0.42317116229896212</v>
+      </c>
+      <c r="L18">
+        <v>0.99960077203044329</v>
+      </c>
+      <c r="M18">
+        <v>0.24840612356867359</v>
+      </c>
+      <c r="N18">
+        <v>56.544381492909572</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+      <c r="C19">
+        <v>2087.487066182759</v>
+      </c>
+      <c r="D19">
+        <v>2087.4870661827699</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>11.864000082015989</v>
+      </c>
+      <c r="H19">
+        <v>-1</v>
+      </c>
+      <c r="I19">
+        <v>-1</v>
+      </c>
+      <c r="J19">
+        <v>-1</v>
+      </c>
+      <c r="K19">
+        <v>0.64722462920157875</v>
+      </c>
+      <c r="L19">
+        <v>0.99910096436126516</v>
+      </c>
+      <c r="M19">
+        <v>0.2938744732007178</v>
+      </c>
+      <c r="N19">
+        <v>56.465239107714069</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>8</v>
+      </c>
+      <c r="C20">
+        <v>1915.380087114828</v>
+      </c>
+      <c r="D20">
+        <v>1915.380087114828</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>13.60099983215332</v>
+      </c>
+      <c r="H20">
+        <v>-1</v>
+      </c>
+      <c r="I20">
+        <v>-1</v>
+      </c>
+      <c r="J20">
+        <v>-1</v>
+      </c>
+      <c r="K20">
+        <v>0.30308584745594119</v>
+      </c>
+      <c r="L20">
+        <v>0.99931632999431019</v>
+      </c>
+      <c r="M20">
+        <v>0.33326875446734389</v>
+      </c>
+      <c r="N20">
+        <v>56.522348955331942</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>9</v>
+      </c>
+      <c r="C21">
+        <v>1976.3520636226669</v>
+      </c>
+      <c r="D21">
+        <v>1976.352063622679</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>7.3320000171661377</v>
+      </c>
+      <c r="H21">
+        <v>-1</v>
+      </c>
+      <c r="I21">
+        <v>-1</v>
+      </c>
+      <c r="J21">
+        <v>-1</v>
+      </c>
+      <c r="K21">
+        <v>0.26379955593918031</v>
+      </c>
+      <c r="L21">
+        <v>0.99898223337214032</v>
+      </c>
+      <c r="M21">
+        <v>0.29485731424121719</v>
+      </c>
+      <c r="N21">
+        <v>56.495610010318053</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>2101.780020727972</v>
+      </c>
+      <c r="D22">
+        <v>2101.780020727972</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>8.434999942779541</v>
+      </c>
+      <c r="H22">
+        <v>-1</v>
+      </c>
+      <c r="I22">
+        <v>-1</v>
+      </c>
+      <c r="J22">
+        <v>-1</v>
+      </c>
+      <c r="K22">
+        <v>0.41073267083189041</v>
+      </c>
+      <c r="L22">
+        <v>0.99920084197125991</v>
+      </c>
+      <c r="M22">
+        <v>0.27983786790461163</v>
+      </c>
+      <c r="N22">
+        <v>56.454019363008129</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23">
+        <v>11</v>
+      </c>
+      <c r="C23">
+        <v>2029.155257821802</v>
+      </c>
+      <c r="D23">
+        <v>2029.155257821802</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>8.2669999599456787</v>
+      </c>
+      <c r="H23">
+        <v>-1</v>
+      </c>
+      <c r="I23">
+        <v>-1</v>
+      </c>
+      <c r="J23">
+        <v>-1</v>
+      </c>
+      <c r="K23">
+        <v>0.4807780345650306</v>
+      </c>
+      <c r="L23">
+        <v>0.99890849381278268</v>
+      </c>
+      <c r="M23">
+        <v>0.28026098600694432</v>
+      </c>
+      <c r="N23">
+        <v>56.374387019983708</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24">
         <v>12</v>
       </c>
-      <c r="B4">
+      <c r="C24">
+        <v>2087.220886095286</v>
+      </c>
+      <c r="D24">
+        <v>2087.2208860952928</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>8.2740001678466797</v>
+      </c>
+      <c r="H24">
+        <v>-1</v>
+      </c>
+      <c r="I24">
+        <v>-1</v>
+      </c>
+      <c r="J24">
+        <v>-1</v>
+      </c>
+      <c r="K24">
+        <v>0.55427523119639255</v>
+      </c>
+      <c r="L24">
+        <v>0.99867988166685662</v>
+      </c>
+      <c r="M24">
+        <v>0.23099268198199749</v>
+      </c>
+      <c r="N24">
+        <v>56.354623563745527</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25">
+        <v>13</v>
+      </c>
+      <c r="C25">
+        <v>2032.5476177500791</v>
+      </c>
+      <c r="D25">
+        <v>2032.547617750088</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>8.5439999103546143</v>
+      </c>
+      <c r="H25">
+        <v>-1</v>
+      </c>
+      <c r="I25">
+        <v>-1</v>
+      </c>
+      <c r="J25">
+        <v>-1</v>
+      </c>
+      <c r="K25">
+        <v>0.36292770604252228</v>
+      </c>
+      <c r="L25">
+        <v>0.9996323085993718</v>
+      </c>
+      <c r="M25">
+        <v>0.28392507515884879</v>
+      </c>
+      <c r="N25">
+        <v>56.442436472075713</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>1977.844892749981</v>
+      </c>
+      <c r="D26">
+        <v>1977.844892749981</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>8.7660000324249268</v>
+      </c>
+      <c r="H26">
+        <v>-1</v>
+      </c>
+      <c r="I26">
+        <v>-1</v>
+      </c>
+      <c r="J26">
+        <v>-1</v>
+      </c>
+      <c r="K26">
+        <v>0.34561295421609722</v>
+      </c>
+      <c r="L26">
+        <v>0.99977314107386528</v>
+      </c>
+      <c r="M26">
+        <v>0.30777659555524378</v>
+      </c>
+      <c r="N26">
+        <v>56.430024451053058</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27">
+        <v>15</v>
+      </c>
+      <c r="C27">
+        <v>2234.0547169191532</v>
+      </c>
+      <c r="D27">
+        <v>2234.0547169191532</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>7.994999885559082</v>
+      </c>
+      <c r="H27">
+        <v>-1</v>
+      </c>
+      <c r="I27">
+        <v>-1</v>
+      </c>
+      <c r="J27">
+        <v>-1</v>
+      </c>
+      <c r="K27">
+        <v>0.54651549659433685</v>
+      </c>
+      <c r="L27">
+        <v>0.9998765593878215</v>
+      </c>
+      <c r="M27">
+        <v>0.27356394093238279</v>
+      </c>
+      <c r="N27">
+        <v>56.446927674395432</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28">
+        <v>16</v>
+      </c>
+      <c r="C28">
+        <v>2115.6141382194951</v>
+      </c>
+      <c r="D28">
+        <v>2115.6141382194951</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>11.10500001907349</v>
+      </c>
+      <c r="H28">
+        <v>-1</v>
+      </c>
+      <c r="I28">
+        <v>-1</v>
+      </c>
+      <c r="J28">
+        <v>-1</v>
+      </c>
+      <c r="K28">
+        <v>0.51283885727699019</v>
+      </c>
+      <c r="L28">
+        <v>0.99975953423225239</v>
+      </c>
+      <c r="M28">
+        <v>0.22004488651054169</v>
+      </c>
+      <c r="N28">
+        <v>56.500566033599917</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29">
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <v>2125.2684262970351</v>
+      </c>
+      <c r="D29">
+        <v>2125.268426297047</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>9.0080001354217529</v>
+      </c>
+      <c r="H29">
+        <v>-1</v>
+      </c>
+      <c r="I29">
+        <v>-1</v>
+      </c>
+      <c r="J29">
+        <v>-1</v>
+      </c>
+      <c r="K29">
+        <v>0.39442046443491119</v>
+      </c>
+      <c r="L29">
+        <v>0.99951186728975971</v>
+      </c>
+      <c r="M29">
+        <v>0.28638874831124778</v>
+      </c>
+      <c r="N29">
+        <v>56.434512624887176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30">
+        <v>18</v>
+      </c>
+      <c r="C30">
+        <v>2137.1368256043061</v>
+      </c>
+      <c r="D30">
+        <v>2137.1368256043061</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>11.13499999046326</v>
+      </c>
+      <c r="H30">
+        <v>-1</v>
+      </c>
+      <c r="I30">
+        <v>-1</v>
+      </c>
+      <c r="J30">
+        <v>-1</v>
+      </c>
+      <c r="K30">
+        <v>0.54178639284467434</v>
+      </c>
+      <c r="L30">
+        <v>0.99954455599268976</v>
+      </c>
+      <c r="M30">
+        <v>0.28764877772158531</v>
+      </c>
+      <c r="N30">
+        <v>56.655101452028013</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31">
+        <v>19</v>
+      </c>
+      <c r="C31">
+        <v>1956.447944427483</v>
+      </c>
+      <c r="D31">
+        <v>1956.447944427508</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>8.0739998817443848</v>
+      </c>
+      <c r="H31">
+        <v>-1</v>
+      </c>
+      <c r="I31">
+        <v>-1</v>
+      </c>
+      <c r="J31">
+        <v>-1</v>
+      </c>
+      <c r="K31">
+        <v>0.47543970251769341</v>
+      </c>
+      <c r="L31">
+        <v>0.99949651109271198</v>
+      </c>
+      <c r="M31">
+        <v>0.30192608787859659</v>
+      </c>
+      <c r="N31">
+        <v>56.571016488691477</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32">
         <v>5</v>
       </c>
-      <c r="C4" s="5">
-        <v>2433.8409802713868</v>
-      </c>
-      <c r="D4" s="5">
-        <v>2433.8409802714</v>
-      </c>
-      <c r="E4" s="3">
-        <f t="shared" ref="E4:E6" si="0">($C$2-C4)/$C$2</f>
-        <v>1.8137446627457348E-2</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0.4309999942779541</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.67046483316948824</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0.24648056968388071</v>
-      </c>
-      <c r="J4" s="5">
-        <v>52.425814767754403</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="C32">
+        <v>2130.1289065423321</v>
+      </c>
+      <c r="D32">
+        <v>2130.1289065423398</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>1.1730000972747801</v>
+      </c>
+      <c r="H32">
+        <v>-1</v>
+      </c>
+      <c r="I32">
+        <v>-1</v>
+      </c>
+      <c r="J32">
+        <v>-1</v>
+      </c>
+      <c r="K32">
+        <v>0.2277643325854572</v>
+      </c>
+      <c r="L32">
+        <v>0.99993189484399359</v>
+      </c>
+      <c r="M32">
+        <v>0.27229890665930162</v>
+      </c>
+      <c r="N32">
+        <v>56.286443687100508</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33">
+        <v>6</v>
+      </c>
+      <c r="C33">
+        <v>2086.2527459782459</v>
+      </c>
+      <c r="D33">
+        <v>2086.2527459782541</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>1.1370000839233401</v>
+      </c>
+      <c r="H33">
+        <v>-1</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+      <c r="J33">
+        <v>-1</v>
+      </c>
+      <c r="K33">
+        <v>0.33999707331252871</v>
+      </c>
+      <c r="L33">
+        <v>0.99957709656505922</v>
+      </c>
+      <c r="M33">
+        <v>0.22639083550779551</v>
+      </c>
+      <c r="N33">
+        <v>56.362654534351663</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>2113.6123432042468</v>
+      </c>
+      <c r="D34">
+        <v>2113.61234320426</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>1.2090001106262209</v>
+      </c>
+      <c r="H34">
+        <v>-1</v>
+      </c>
+      <c r="I34">
+        <v>-1</v>
+      </c>
+      <c r="J34">
+        <v>-1</v>
+      </c>
+      <c r="K34">
+        <v>0.36827790410553563</v>
+      </c>
+      <c r="L34">
+        <v>0.99959942169119098</v>
+      </c>
+      <c r="M34">
+        <v>0.27452650684053992</v>
+      </c>
+      <c r="N34">
+        <v>56.098871461032388</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>1963.370737269446</v>
+      </c>
+      <c r="D35">
+        <v>1963.370737269456</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>1.135999917984009</v>
+      </c>
+      <c r="H35">
+        <v>-1</v>
+      </c>
+      <c r="I35">
+        <v>-1</v>
+      </c>
+      <c r="J35">
+        <v>-1</v>
+      </c>
+      <c r="K35">
+        <v>0.21150125016179791</v>
+      </c>
+      <c r="L35">
+        <v>0.99911840708868782</v>
+      </c>
+      <c r="M35">
+        <v>0.28337358550080283</v>
+      </c>
+      <c r="N35">
+        <v>56.602734749257017</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36">
+        <v>9</v>
+      </c>
+      <c r="C36">
+        <v>2038.825287109348</v>
+      </c>
+      <c r="D36">
+        <v>2038.825287109348</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>1.218999862670898</v>
+      </c>
+      <c r="H36">
+        <v>-1</v>
+      </c>
+      <c r="I36">
+        <v>-1</v>
+      </c>
+      <c r="J36">
+        <v>-1</v>
+      </c>
+      <c r="K36">
+        <v>0.22892206566069909</v>
+      </c>
+      <c r="L36">
+        <v>0.99989175735709479</v>
+      </c>
+      <c r="M36">
+        <v>0.25194448035495393</v>
+      </c>
+      <c r="N36">
+        <v>56.281881629417157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37">
+        <v>10</v>
+      </c>
+      <c r="C37">
+        <v>2122.9052826934189</v>
+      </c>
+      <c r="D37">
+        <v>2122.9052826934189</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>1.203000068664551</v>
+      </c>
+      <c r="H37">
+        <v>-1</v>
+      </c>
+      <c r="I37">
+        <v>-1</v>
+      </c>
+      <c r="J37">
+        <v>-1</v>
+      </c>
+      <c r="K37">
+        <v>0.34901748034551888</v>
+      </c>
+      <c r="L37">
+        <v>0.99992763942602747</v>
+      </c>
+      <c r="M37">
+        <v>0.2515103279838089</v>
+      </c>
+      <c r="N37">
+        <v>56.438374054309882</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38">
+        <v>11</v>
+      </c>
+      <c r="C38">
+        <v>2073.853725622861</v>
+      </c>
+      <c r="D38">
+        <v>2073.8537256228778</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>1.197999954223633</v>
+      </c>
+      <c r="H38">
+        <v>-1</v>
+      </c>
+      <c r="I38">
+        <v>-1</v>
+      </c>
+      <c r="J38">
+        <v>-1</v>
+      </c>
+      <c r="K38">
+        <v>0.32792073847512943</v>
+      </c>
+      <c r="L38">
+        <v>0.99930280289808848</v>
+      </c>
+      <c r="M38">
+        <v>0.26400592600484152</v>
+      </c>
+      <c r="N38">
+        <v>56.349134251770757</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39">
+        <v>12</v>
+      </c>
+      <c r="C39">
+        <v>2110.5694590938551</v>
+      </c>
+      <c r="D39">
+        <v>2110.569459093877</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>1.26800012588501</v>
+      </c>
+      <c r="H39">
+        <v>-1</v>
+      </c>
+      <c r="I39">
+        <v>-1</v>
+      </c>
+      <c r="J39">
+        <v>-1</v>
+      </c>
+      <c r="K39">
+        <v>0.29024113719291389</v>
+      </c>
+      <c r="L39">
+        <v>0.99916998830956982</v>
+      </c>
+      <c r="M39">
+        <v>0.21236827719238721</v>
+      </c>
+      <c r="N39">
+        <v>56.377119091517379</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40">
         <v>13</v>
       </c>
-      <c r="B5">
+      <c r="C40">
+        <v>2065.6698860234701</v>
+      </c>
+      <c r="D40">
+        <v>2065.6698860234701</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>1.263999938964844</v>
+      </c>
+      <c r="H40">
+        <v>-1</v>
+      </c>
+      <c r="I40">
+        <v>-1</v>
+      </c>
+      <c r="J40">
+        <v>-1</v>
+      </c>
+      <c r="K40">
+        <v>0.26110267439861612</v>
+      </c>
+      <c r="L40">
+        <v>0.99999901889703924</v>
+      </c>
+      <c r="M40">
+        <v>0.25776745260807671</v>
+      </c>
+      <c r="N40">
+        <v>56.203346616474228</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>2001.0228932687451</v>
+      </c>
+      <c r="D41">
+        <v>2001.0228932687451</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>1.217999935150146</v>
+      </c>
+      <c r="H41">
+        <v>-1</v>
+      </c>
+      <c r="I41">
+        <v>-1</v>
+      </c>
+      <c r="J41">
+        <v>-1</v>
+      </c>
+      <c r="K41">
+        <v>0.20894424304202711</v>
+      </c>
+      <c r="L41">
+        <v>0.99968989256820029</v>
+      </c>
+      <c r="M41">
+        <v>0.27291597449811678</v>
+      </c>
+      <c r="N41">
+        <v>56.286923282514607</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42">
+        <v>15</v>
+      </c>
+      <c r="C42">
+        <v>2280.5269813677301</v>
+      </c>
+      <c r="D42">
+        <v>2280.526981367756</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>1.28600001335144</v>
+      </c>
+      <c r="H42">
+        <v>-1</v>
+      </c>
+      <c r="I42">
+        <v>-1</v>
+      </c>
+      <c r="J42">
+        <v>-1</v>
+      </c>
+      <c r="K42">
+        <v>0.40100416796612331</v>
+      </c>
+      <c r="L42">
+        <v>0.99997113420916584</v>
+      </c>
+      <c r="M42">
+        <v>0.23151766320906511</v>
+      </c>
+      <c r="N42">
+        <v>56.144726823470997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>2116.8410833117841</v>
+      </c>
+      <c r="D43">
+        <v>2116.8410833117841</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>1.250999927520752</v>
+      </c>
+      <c r="H43">
+        <v>-1</v>
+      </c>
+      <c r="I43">
+        <v>-1</v>
+      </c>
+      <c r="J43">
+        <v>-1</v>
+      </c>
+      <c r="K43">
+        <v>0.30526611412590521</v>
+      </c>
+      <c r="L43">
+        <v>0.99962570090931269</v>
+      </c>
+      <c r="M43">
+        <v>0.21055387327656949</v>
+      </c>
+      <c r="N43">
+        <v>56.360277303833932</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>2145.232816500813</v>
+      </c>
+      <c r="D44">
+        <v>2145.2328165008348</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>1.204999685287476</v>
+      </c>
+      <c r="H44">
+        <v>-1</v>
+      </c>
+      <c r="I44">
+        <v>-1</v>
+      </c>
+      <c r="J44">
+        <v>-1</v>
+      </c>
+      <c r="K44">
+        <v>0.29587689797586442</v>
+      </c>
+      <c r="L44">
+        <v>0.99979100838303547</v>
+      </c>
+      <c r="M44">
+        <v>0.25053230346362249</v>
+      </c>
+      <c r="N44">
+        <v>56.4052142233814</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45">
+        <v>18</v>
+      </c>
+      <c r="C45">
+        <v>2168.2953232477421</v>
+      </c>
+      <c r="D45">
+        <v>2168.2953232477421</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1.174999952316284</v>
+      </c>
+      <c r="H45">
+        <v>-1</v>
+      </c>
+      <c r="I45">
+        <v>-1</v>
+      </c>
+      <c r="J45">
+        <v>-1</v>
+      </c>
+      <c r="K45">
+        <v>0.39462514242671248</v>
+      </c>
+      <c r="L45">
+        <v>0.99968283614034359</v>
+      </c>
+      <c r="M45">
+        <v>0.2646561687748345</v>
+      </c>
+      <c r="N45">
+        <v>56.359915306830331</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46">
+        <v>19</v>
+      </c>
+      <c r="C46">
+        <v>1967.0658237226301</v>
+      </c>
+      <c r="D46">
+        <v>1967.0658237226439</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>1.1999998092651369</v>
+      </c>
+      <c r="H46">
+        <v>-1</v>
+      </c>
+      <c r="I46">
+        <v>-1</v>
+      </c>
+      <c r="J46">
+        <v>-1</v>
+      </c>
+      <c r="K46">
+        <v>0.2039717158535124</v>
+      </c>
+      <c r="L46">
+        <v>0.99961151669430537</v>
+      </c>
+      <c r="M46">
+        <v>0.27025532655628609</v>
+      </c>
+      <c r="N46">
+        <v>56.360779637078238</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47">
         <v>5</v>
       </c>
-      <c r="C5" s="5">
-        <v>1557.752131379995</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1557.9061630526739</v>
-      </c>
-      <c r="E5" s="3">
-        <f t="shared" si="0"/>
-        <v>0.37157008299378091</v>
-      </c>
-      <c r="F5" s="5">
-        <v>3.074151992797852</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.30284942379632601</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.99872418402677465</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0.28625799886427178</v>
-      </c>
-      <c r="J5" s="5">
-        <v>57.480231763701887</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="C47">
+        <v>1720.018387746693</v>
+      </c>
+      <c r="D47">
+        <v>1720.0183877466941</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>15.38379001617432</v>
+      </c>
+      <c r="G47">
+        <v>3</v>
+      </c>
+      <c r="H47">
+        <v>-1</v>
+      </c>
+      <c r="I47">
+        <v>-1</v>
+      </c>
+      <c r="J47">
+        <v>-1</v>
+      </c>
+      <c r="K47">
+        <v>0.17586188425864099</v>
+      </c>
+      <c r="L47">
+        <v>0.99902508379642097</v>
+      </c>
+      <c r="M47">
+        <v>0.28949939565334809</v>
+      </c>
+      <c r="N47">
+        <v>59.999999999999993</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48">
+        <v>6</v>
+      </c>
+      <c r="C48">
+        <v>1706.067853553956</v>
+      </c>
+      <c r="D48">
+        <v>1706.0678535539721</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>15.668661594390869</v>
+      </c>
+      <c r="G48">
+        <v>3</v>
+      </c>
+      <c r="H48">
+        <v>-1</v>
+      </c>
+      <c r="I48">
+        <v>-1</v>
+      </c>
+      <c r="J48">
+        <v>-1</v>
+      </c>
+      <c r="K48">
+        <v>0.21445042508508219</v>
+      </c>
+      <c r="L48">
+        <v>0.99922046475047732</v>
+      </c>
+      <c r="M48">
+        <v>0.25399233793355791</v>
+      </c>
+      <c r="N48">
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49">
+        <v>7</v>
+      </c>
+      <c r="C49">
+        <v>1709.6044922885869</v>
+      </c>
+      <c r="D49">
+        <v>1709.604492288594</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>20.511092901229858</v>
+      </c>
+      <c r="G49">
+        <v>4</v>
+      </c>
+      <c r="H49">
+        <v>-1</v>
+      </c>
+      <c r="I49">
+        <v>-1</v>
+      </c>
+      <c r="J49">
+        <v>-1</v>
+      </c>
+      <c r="K49">
+        <v>0.51692093474912693</v>
+      </c>
+      <c r="L49">
+        <v>0.99835551891160657</v>
+      </c>
+      <c r="M49">
+        <v>0.29554273470513248</v>
+      </c>
+      <c r="N49">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50">
+        <v>8</v>
+      </c>
+      <c r="C50">
+        <v>1642.047876212127</v>
+      </c>
+      <c r="D50">
+        <v>1642.047876212137</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>20.3364577293396</v>
+      </c>
+      <c r="G50">
+        <v>3</v>
+      </c>
+      <c r="H50">
+        <v>-1</v>
+      </c>
+      <c r="I50">
+        <v>-1</v>
+      </c>
+      <c r="J50">
+        <v>-1</v>
+      </c>
+      <c r="K50">
+        <v>0.16687833976375341</v>
+      </c>
+      <c r="L50">
+        <v>0.99914377720583469</v>
+      </c>
+      <c r="M50">
+        <v>0.32689683894410831</v>
+      </c>
+      <c r="N50">
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51">
+        <v>9</v>
+      </c>
+      <c r="C51">
+        <v>1661.134187154581</v>
+      </c>
+      <c r="D51">
+        <v>1661.134187154586</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>22.112881183624271</v>
+      </c>
+      <c r="G51">
+        <v>6</v>
+      </c>
+      <c r="H51">
+        <v>-1</v>
+      </c>
+      <c r="I51">
+        <v>-1</v>
+      </c>
+      <c r="J51">
+        <v>-1</v>
+      </c>
+      <c r="K51">
+        <v>0.21270109710055901</v>
+      </c>
+      <c r="L51">
+        <v>0.99844991191758603</v>
+      </c>
+      <c r="M51">
+        <v>0.27945828742152401</v>
+      </c>
+      <c r="N51">
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52">
+        <v>10</v>
+      </c>
+      <c r="C52">
+        <v>1703.598307858397</v>
+      </c>
+      <c r="D52">
+        <v>1703.598307858397</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>12.46955347061157</v>
+      </c>
+      <c r="G52">
+        <v>2</v>
+      </c>
+      <c r="H52">
+        <v>-1</v>
+      </c>
+      <c r="I52">
+        <v>-1</v>
+      </c>
+      <c r="J52">
+        <v>-1</v>
+      </c>
+      <c r="K52">
+        <v>0.21454520357763951</v>
+      </c>
+      <c r="L52">
+        <v>0.99919150257970801</v>
+      </c>
+      <c r="M52">
+        <v>0.28575995315789599</v>
+      </c>
+      <c r="N52">
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53">
+        <v>11</v>
+      </c>
+      <c r="C53">
+        <v>1684.7199445989829</v>
+      </c>
+      <c r="D53">
+        <v>1684.7199445989829</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>13.199843645095831</v>
+      </c>
+      <c r="G53">
+        <v>2</v>
+      </c>
+      <c r="H53">
+        <v>-1</v>
+      </c>
+      <c r="I53">
+        <v>-1</v>
+      </c>
+      <c r="J53">
+        <v>-1</v>
+      </c>
+      <c r="K53">
+        <v>0.19671581917096731</v>
+      </c>
+      <c r="L53">
+        <v>0.99880325759245481</v>
+      </c>
+      <c r="M53">
+        <v>0.2890560619632484</v>
+      </c>
+      <c r="N53">
+        <v>59.999999999999993</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54">
         <v>12</v>
       </c>
-      <c r="B6">
+      <c r="C54">
+        <v>1730.821407708333</v>
+      </c>
+      <c r="D54">
+        <v>1730.821407708341</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>13.43324255943298</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54">
+        <v>-1</v>
+      </c>
+      <c r="I54">
+        <v>-1</v>
+      </c>
+      <c r="J54">
+        <v>-1</v>
+      </c>
+      <c r="K54">
+        <v>0.20604721321709321</v>
+      </c>
+      <c r="L54">
+        <v>0.99884187580779737</v>
+      </c>
+      <c r="M54">
+        <v>0.23590853363604339</v>
+      </c>
+      <c r="N54">
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55">
+        <v>13</v>
+      </c>
+      <c r="C55">
+        <v>1678.066864342147</v>
+      </c>
+      <c r="D55">
+        <v>1678.066864342147</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>15.241834878921511</v>
+      </c>
+      <c r="G55">
+        <v>3</v>
+      </c>
+      <c r="H55">
+        <v>-1</v>
+      </c>
+      <c r="I55">
+        <v>-1</v>
+      </c>
+      <c r="J55">
+        <v>-1</v>
+      </c>
+      <c r="K55">
+        <v>0.23610598637339819</v>
+      </c>
+      <c r="L55">
+        <v>0.99928952698654006</v>
+      </c>
+      <c r="M55">
+        <v>0.30021501024671582</v>
+      </c>
+      <c r="N55">
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B56">
+        <v>14</v>
+      </c>
+      <c r="C56">
+        <v>1652.5304798788791</v>
+      </c>
+      <c r="D56">
+        <v>1652.5304798788791</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>18.524370193481449</v>
+      </c>
+      <c r="G56">
+        <v>4</v>
+      </c>
+      <c r="H56">
+        <v>-1</v>
+      </c>
+      <c r="I56">
+        <v>-1</v>
+      </c>
+      <c r="J56">
+        <v>-1</v>
+      </c>
+      <c r="K56">
+        <v>0.19747050306514871</v>
+      </c>
+      <c r="L56">
+        <v>0.99977708893252659</v>
+      </c>
+      <c r="M56">
+        <v>0.29236000506519871</v>
+      </c>
+      <c r="N56">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57">
+        <v>15</v>
+      </c>
+      <c r="C57">
+        <v>1817.2468663710499</v>
+      </c>
+      <c r="D57">
+        <v>1817.246866371052</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>15.31238484382629</v>
+      </c>
+      <c r="G57">
+        <v>3</v>
+      </c>
+      <c r="H57">
+        <v>-1</v>
+      </c>
+      <c r="I57">
+        <v>-1</v>
+      </c>
+      <c r="J57">
+        <v>-1</v>
+      </c>
+      <c r="K57">
+        <v>0.42671690344414859</v>
+      </c>
+      <c r="L57">
+        <v>0.99931773489150977</v>
+      </c>
+      <c r="M57">
+        <v>0.28125688733016818</v>
+      </c>
+      <c r="N57">
+        <v>59.999999999999993</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>17</v>
+      </c>
+      <c r="B58">
+        <v>16</v>
+      </c>
+      <c r="C58">
+        <v>1702.081902585237</v>
+      </c>
+      <c r="D58">
+        <v>1702.081902585237</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>19.497958660125729</v>
+      </c>
+      <c r="G58">
+        <v>3</v>
+      </c>
+      <c r="H58">
+        <v>-1</v>
+      </c>
+      <c r="I58">
+        <v>-1</v>
+      </c>
+      <c r="J58">
+        <v>-1</v>
+      </c>
+      <c r="K58">
+        <v>0.21829927179880429</v>
+      </c>
+      <c r="L58">
+        <v>0.99953712997977995</v>
+      </c>
+      <c r="M58">
+        <v>0.23479009169041429</v>
+      </c>
+      <c r="N58">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>17</v>
+      </c>
+      <c r="B59">
+        <v>17</v>
+      </c>
+      <c r="C59">
+        <v>1733.6632630084271</v>
+      </c>
+      <c r="D59">
+        <v>1733.66326300843</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>16.12336707115173</v>
+      </c>
+      <c r="G59">
+        <v>3</v>
+      </c>
+      <c r="H59">
+        <v>-1</v>
+      </c>
+      <c r="I59">
+        <v>-1</v>
+      </c>
+      <c r="J59">
+        <v>-1</v>
+      </c>
+      <c r="K59">
+        <v>0.20028079000240179</v>
+      </c>
+      <c r="L59">
+        <v>0.99853036201746637</v>
+      </c>
+      <c r="M59">
+        <v>0.26022306616026702</v>
+      </c>
+      <c r="N59">
+        <v>60.000000000000007</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>17</v>
+      </c>
+      <c r="B60">
+        <v>18</v>
+      </c>
+      <c r="C60">
+        <v>1736.1482745073679</v>
+      </c>
+      <c r="D60">
+        <v>1736.1482745073711</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>16.234471797943119</v>
+      </c>
+      <c r="G60">
+        <v>2</v>
+      </c>
+      <c r="H60">
+        <v>-1</v>
+      </c>
+      <c r="I60">
+        <v>-1</v>
+      </c>
+      <c r="J60">
+        <v>-1</v>
+      </c>
+      <c r="K60">
+        <v>0.42847427802466848</v>
+      </c>
+      <c r="L60">
+        <v>0.9987705565046866</v>
+      </c>
+      <c r="M60">
+        <v>0.31198946739337702</v>
+      </c>
+      <c r="N60">
+        <v>59.999999999999993</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61">
+        <v>19</v>
+      </c>
+      <c r="C61">
+        <v>1652.471982380966</v>
+      </c>
+      <c r="D61">
+        <v>1652.471982380966</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>14.00003671646118</v>
+      </c>
+      <c r="G61">
+        <v>2</v>
+      </c>
+      <c r="H61">
+        <v>-1</v>
+      </c>
+      <c r="I61">
+        <v>-1</v>
+      </c>
+      <c r="J61">
+        <v>-1</v>
+      </c>
+      <c r="K61">
+        <v>0.35676664138594449</v>
+      </c>
+      <c r="L61">
+        <v>0.99916740576260221</v>
+      </c>
+      <c r="M61">
+        <v>0.29083235003825109</v>
+      </c>
+      <c r="N61">
+        <v>59.990525507128417</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62">
         <v>5</v>
       </c>
-      <c r="C6" s="5">
-        <v>2439.8151679024108</v>
-      </c>
-      <c r="D6" s="5">
-        <v>2440.0538413675472</v>
-      </c>
-      <c r="E6" s="3">
-        <f t="shared" si="0"/>
-        <v>1.5727333900589769E-2</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.37700009346008301</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.69107400694141541</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0.24982453568027879</v>
-      </c>
-      <c r="J6" s="5">
-        <v>52.563154338072167</v>
+      <c r="C62">
+        <v>2131.2125523258419</v>
+      </c>
+      <c r="D62">
+        <v>2131.4139939054348</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>126.7355215549469</v>
+      </c>
+      <c r="H62">
+        <v>-1</v>
+      </c>
+      <c r="I62">
+        <v>-1</v>
+      </c>
+      <c r="J62">
+        <v>-1</v>
+      </c>
+      <c r="K62">
+        <v>0.23057693315189279</v>
+      </c>
+      <c r="L62">
+        <v>0.9999323032676356</v>
+      </c>
+      <c r="M62">
+        <v>0.27361607558633583</v>
+      </c>
+      <c r="N62">
+        <v>56.351563844950213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+      <c r="C63">
+        <v>2086.8889489425992</v>
+      </c>
+      <c r="D63">
+        <v>2087.0582659939059</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>177.18513512611389</v>
+      </c>
+      <c r="H63">
+        <v>-1</v>
+      </c>
+      <c r="I63">
+        <v>-1</v>
+      </c>
+      <c r="J63">
+        <v>-1</v>
+      </c>
+      <c r="K63">
+        <v>0.3315383250599177</v>
+      </c>
+      <c r="L63">
+        <v>0.99957984824187995</v>
+      </c>
+      <c r="M63">
+        <v>0.22598768270072209</v>
+      </c>
+      <c r="N63">
+        <v>56.365185663662849</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64">
+        <v>7</v>
+      </c>
+      <c r="C64">
+        <v>2115.2596269638971</v>
+      </c>
+      <c r="D64">
+        <v>2115.4256901500812</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>869.08058071136475</v>
+      </c>
+      <c r="H64">
+        <v>-1</v>
+      </c>
+      <c r="I64">
+        <v>-1</v>
+      </c>
+      <c r="J64">
+        <v>-1</v>
+      </c>
+      <c r="K64">
+        <v>0.36986061227304612</v>
+      </c>
+      <c r="L64">
+        <v>0.99966003852945373</v>
+      </c>
+      <c r="M64">
+        <v>0.27320052929017019</v>
+      </c>
+      <c r="N64">
+        <v>56.093283705502863</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65">
+        <v>8</v>
+      </c>
+      <c r="C65">
+        <v>1964.026955663853</v>
+      </c>
+      <c r="D65">
+        <v>1964.2201718459039</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>179.7016530036926</v>
+      </c>
+      <c r="H65">
+        <v>-1</v>
+      </c>
+      <c r="I65">
+        <v>-1</v>
+      </c>
+      <c r="J65">
+        <v>-1</v>
+      </c>
+      <c r="K65">
+        <v>0.21374577675706019</v>
+      </c>
+      <c r="L65">
+        <v>0.99926916955162182</v>
+      </c>
+      <c r="M65">
+        <v>0.28285381410667698</v>
+      </c>
+      <c r="N65">
+        <v>56.595659469598388</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66">
+        <v>9</v>
+      </c>
+      <c r="C66">
+        <v>2039.2981462657369</v>
+      </c>
+      <c r="D66">
+        <v>2039.4997740809681</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>135.19698476791379</v>
+      </c>
+      <c r="H66">
+        <v>-1</v>
+      </c>
+      <c r="I66">
+        <v>-1</v>
+      </c>
+      <c r="J66">
+        <v>-1</v>
+      </c>
+      <c r="K66">
+        <v>0.23138222048673371</v>
+      </c>
+      <c r="L66">
+        <v>0.99989204008642507</v>
+      </c>
+      <c r="M66">
+        <v>0.25292470949437112</v>
+      </c>
+      <c r="N66">
+        <v>56.260638923676993</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67">
+        <v>10</v>
+      </c>
+      <c r="C67">
+        <v>2124.5288451568108</v>
+      </c>
+      <c r="D67">
+        <v>2124.7306983080098</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>413.56189513206482</v>
+      </c>
+      <c r="H67">
+        <v>-1</v>
+      </c>
+      <c r="I67">
+        <v>-1</v>
+      </c>
+      <c r="J67">
+        <v>-1</v>
+      </c>
+      <c r="K67">
+        <v>0.35783894338807948</v>
+      </c>
+      <c r="L67">
+        <v>0.99980467269776097</v>
+      </c>
+      <c r="M67">
+        <v>0.25255340659520381</v>
+      </c>
+      <c r="N67">
+        <v>56.473832407622758</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68">
+        <v>11</v>
+      </c>
+      <c r="C68">
+        <v>2078.1071595199851</v>
+      </c>
+      <c r="D68">
+        <v>2078.289789952697</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>837.37139630317688</v>
+      </c>
+      <c r="H68">
+        <v>-1</v>
+      </c>
+      <c r="I68">
+        <v>-1</v>
+      </c>
+      <c r="J68">
+        <v>-1</v>
+      </c>
+      <c r="K68">
+        <v>0.32931052273771699</v>
+      </c>
+      <c r="L68">
+        <v>0.99926745206471268</v>
+      </c>
+      <c r="M68">
+        <v>0.2636577931478904</v>
+      </c>
+      <c r="N68">
+        <v>56.342330552441382</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>18</v>
+      </c>
+      <c r="B69">
+        <v>12</v>
+      </c>
+      <c r="C69">
+        <v>2113.5458093665502</v>
+      </c>
+      <c r="D69">
+        <v>2113.7335395822029</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>958.946852684021</v>
+      </c>
+      <c r="H69">
+        <v>-1</v>
+      </c>
+      <c r="I69">
+        <v>-1</v>
+      </c>
+      <c r="J69">
+        <v>-1</v>
+      </c>
+      <c r="K69">
+        <v>0.29578256633496403</v>
+      </c>
+      <c r="L69">
+        <v>0.99895395516983532</v>
+      </c>
+      <c r="M69">
+        <v>0.21597787925892931</v>
+      </c>
+      <c r="N69">
+        <v>56.347113822177008</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>18</v>
+      </c>
+      <c r="B70">
+        <v>13</v>
+      </c>
+      <c r="C70">
+        <v>2067.8141355193729</v>
+      </c>
+      <c r="D70">
+        <v>2068.009457517383</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>616.52336812019348</v>
+      </c>
+      <c r="H70">
+        <v>-1</v>
+      </c>
+      <c r="I70">
+        <v>-1</v>
+      </c>
+      <c r="J70">
+        <v>-1</v>
+      </c>
+      <c r="K70">
+        <v>0.25973635551736191</v>
+      </c>
+      <c r="L70">
+        <v>0.99999664544165123</v>
+      </c>
+      <c r="M70">
+        <v>0.2475269433638192</v>
+      </c>
+      <c r="N70">
+        <v>56.10753924996915</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>18</v>
+      </c>
+      <c r="B71">
+        <v>14</v>
+      </c>
+      <c r="C71">
+        <v>2009.8288053956451</v>
+      </c>
+      <c r="D71">
+        <v>2009.965768524379</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>113.2442257404327</v>
+      </c>
+      <c r="H71">
+        <v>-1</v>
+      </c>
+      <c r="I71">
+        <v>-1</v>
+      </c>
+      <c r="J71">
+        <v>-1</v>
+      </c>
+      <c r="K71">
+        <v>0.36124190116505528</v>
+      </c>
+      <c r="L71">
+        <v>0.9996757870502776</v>
+      </c>
+      <c r="M71">
+        <v>0.27899571679704749</v>
+      </c>
+      <c r="N71">
+        <v>56.251829959294561</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>18</v>
+      </c>
+      <c r="B72">
+        <v>15</v>
+      </c>
+      <c r="C72">
+        <v>2282.3222424307769</v>
+      </c>
+      <c r="D72">
+        <v>2282.4759054199549</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>969.12566208839417</v>
+      </c>
+      <c r="H72">
+        <v>-1</v>
+      </c>
+      <c r="I72">
+        <v>-1</v>
+      </c>
+      <c r="J72">
+        <v>-1</v>
+      </c>
+      <c r="K72">
+        <v>0.40159287772221558</v>
+      </c>
+      <c r="L72">
+        <v>0.99997120111810212</v>
+      </c>
+      <c r="M72">
+        <v>0.22929437545466419</v>
+      </c>
+      <c r="N72">
+        <v>56.093599613492202</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73">
+        <v>16</v>
+      </c>
+      <c r="C73">
+        <v>2119.8460785022398</v>
+      </c>
+      <c r="D73">
+        <v>2120.0501507938452</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>355.97341179847717</v>
+      </c>
+      <c r="H73">
+        <v>-1</v>
+      </c>
+      <c r="I73">
+        <v>-1</v>
+      </c>
+      <c r="J73">
+        <v>-1</v>
+      </c>
+      <c r="K73">
+        <v>0.30667249988192768</v>
+      </c>
+      <c r="L73">
+        <v>0.99962745747649107</v>
+      </c>
+      <c r="M73">
+        <v>0.21536388739784751</v>
+      </c>
+      <c r="N73">
+        <v>56.386110473832858</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B74">
+        <v>17</v>
+      </c>
+      <c r="C74">
+        <v>2153.0158397177761</v>
+      </c>
+      <c r="D74">
+        <v>2153.1796213175271</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>151.02000594139099</v>
+      </c>
+      <c r="H74">
+        <v>-1</v>
+      </c>
+      <c r="I74">
+        <v>-1</v>
+      </c>
+      <c r="J74">
+        <v>-1</v>
+      </c>
+      <c r="K74">
+        <v>0.3089649079955436</v>
+      </c>
+      <c r="L74">
+        <v>0.99977382644083035</v>
+      </c>
+      <c r="M74">
+        <v>0.24880541122357289</v>
+      </c>
+      <c r="N74">
+        <v>56.392266751323078</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>18</v>
+      </c>
+      <c r="B75">
+        <v>18</v>
+      </c>
+      <c r="C75">
+        <v>2171.3003476914009</v>
+      </c>
+      <c r="D75">
+        <v>2171.4998619964949</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>787.93007707595825</v>
+      </c>
+      <c r="H75">
+        <v>-1</v>
+      </c>
+      <c r="I75">
+        <v>-1</v>
+      </c>
+      <c r="J75">
+        <v>-1</v>
+      </c>
+      <c r="K75">
+        <v>0.39667270263768922</v>
+      </c>
+      <c r="L75">
+        <v>0.99977250713337718</v>
+      </c>
+      <c r="M75">
+        <v>0.26699363661763098</v>
+      </c>
+      <c r="N75">
+        <v>56.325874399493181</v>
+      </c>
+    </row>
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>18</v>
+      </c>
+      <c r="B76">
+        <v>19</v>
+      </c>
+      <c r="C76">
+        <v>1968.420148246845</v>
+      </c>
+      <c r="D76">
+        <v>1968.614170112774</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>390.34646797180181</v>
+      </c>
+      <c r="H76">
+        <v>-1</v>
+      </c>
+      <c r="I76">
+        <v>-1</v>
+      </c>
+      <c r="J76">
+        <v>-1</v>
+      </c>
+      <c r="K76">
+        <v>0.20430781711179549</v>
+      </c>
+      <c r="L76">
+        <v>0.99960772567779632</v>
+      </c>
+      <c r="M76">
+        <v>0.27372106338919672</v>
+      </c>
+      <c r="N76">
+        <v>56.340850973082063</v>
+      </c>
+    </row>
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77">
+        <v>5</v>
+      </c>
+      <c r="C77">
+        <v>1777.2825992777571</v>
+      </c>
+      <c r="D77">
+        <v>1777.4103673570839</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>40.904355764389038</v>
+      </c>
+      <c r="G77">
+        <v>3</v>
+      </c>
+      <c r="H77">
+        <v>-1</v>
+      </c>
+      <c r="I77">
+        <v>-1</v>
+      </c>
+      <c r="J77">
+        <v>-1</v>
+      </c>
+      <c r="K77">
+        <v>0.19312374569023871</v>
+      </c>
+      <c r="L77">
+        <v>0.99909172653370426</v>
+      </c>
+      <c r="M77">
+        <v>0.29106326487036033</v>
+      </c>
+      <c r="N77">
+        <v>59.338710881434643</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>19</v>
+      </c>
+      <c r="B78">
+        <v>6</v>
+      </c>
+      <c r="C78">
+        <v>1730.3012510547101</v>
+      </c>
+      <c r="D78">
+        <v>1730.444687348057</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>41.252920389175422</v>
+      </c>
+      <c r="G78">
+        <v>3</v>
+      </c>
+      <c r="H78">
+        <v>-1</v>
+      </c>
+      <c r="I78">
+        <v>-1</v>
+      </c>
+      <c r="J78">
+        <v>-1</v>
+      </c>
+      <c r="K78">
+        <v>0.22834656784020299</v>
+      </c>
+      <c r="L78">
+        <v>0.99924737137468378</v>
+      </c>
+      <c r="M78">
+        <v>0.25359172109979311</v>
+      </c>
+      <c r="N78">
+        <v>59.699407240287762</v>
+      </c>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79">
+        <v>7</v>
+      </c>
+      <c r="C79">
+        <v>1787.4091905123121</v>
+      </c>
+      <c r="D79">
+        <v>1787.5819573589331</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>45.751142740249627</v>
+      </c>
+      <c r="G79">
+        <v>4</v>
+      </c>
+      <c r="H79">
+        <v>-1</v>
+      </c>
+      <c r="I79">
+        <v>-1</v>
+      </c>
+      <c r="J79">
+        <v>-1</v>
+      </c>
+      <c r="K79">
+        <v>0.55526703263626132</v>
+      </c>
+      <c r="L79">
+        <v>0.99859630207272043</v>
+      </c>
+      <c r="M79">
+        <v>0.28386043525857968</v>
+      </c>
+      <c r="N79">
+        <v>58.569882120359068</v>
+      </c>
+    </row>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>19</v>
+      </c>
+      <c r="B80">
+        <v>8</v>
+      </c>
+      <c r="C80">
+        <v>1668.7038623102089</v>
+      </c>
+      <c r="D80">
+        <v>1668.8483073406489</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>55.363762617111213</v>
+      </c>
+      <c r="G80">
+        <v>3</v>
+      </c>
+      <c r="H80">
+        <v>-1</v>
+      </c>
+      <c r="I80">
+        <v>-1</v>
+      </c>
+      <c r="J80">
+        <v>-1</v>
+      </c>
+      <c r="K80">
+        <v>0.1774417158391462</v>
+      </c>
+      <c r="L80">
+        <v>0.99917090619769988</v>
+      </c>
+      <c r="M80">
+        <v>0.32331014221887427</v>
+      </c>
+      <c r="N80">
+        <v>59.448962704545842</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>19</v>
+      </c>
+      <c r="B81">
+        <v>9</v>
+      </c>
+      <c r="C81">
+        <v>1691.9635832198339</v>
+      </c>
+      <c r="D81">
+        <v>1692.119692594461</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>48.241856575012207</v>
+      </c>
+      <c r="G81">
+        <v>6</v>
+      </c>
+      <c r="H81">
+        <v>-1</v>
+      </c>
+      <c r="I81">
+        <v>-1</v>
+      </c>
+      <c r="J81">
+        <v>-1</v>
+      </c>
+      <c r="K81">
+        <v>0.22137197483089391</v>
+      </c>
+      <c r="L81">
+        <v>0.99856428812680631</v>
+      </c>
+      <c r="M81">
+        <v>0.25585891071060263</v>
+      </c>
+      <c r="N81">
+        <v>59.588861284574591</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>19</v>
+      </c>
+      <c r="B82">
+        <v>10</v>
+      </c>
+      <c r="C82">
+        <v>1738.264892219843</v>
+      </c>
+      <c r="D82">
+        <v>1738.4346220487889</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>29.264552354812619</v>
+      </c>
+      <c r="G82">
+        <v>2</v>
+      </c>
+      <c r="H82">
+        <v>-1</v>
+      </c>
+      <c r="I82">
+        <v>-1</v>
+      </c>
+      <c r="J82">
+        <v>-1</v>
+      </c>
+      <c r="K82">
+        <v>0.23804413103030811</v>
+      </c>
+      <c r="L82">
+        <v>0.99923918630164454</v>
+      </c>
+      <c r="M82">
+        <v>0.28176008370676892</v>
+      </c>
+      <c r="N82">
+        <v>59.59120154056361</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>19</v>
+      </c>
+      <c r="B83">
+        <v>11</v>
+      </c>
+      <c r="C83">
+        <v>1707.0608240709639</v>
+      </c>
+      <c r="D83">
+        <v>1707.229142285343</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>33.610151052474983</v>
+      </c>
+      <c r="G83">
+        <v>2</v>
+      </c>
+      <c r="H83">
+        <v>-1</v>
+      </c>
+      <c r="I83">
+        <v>-1</v>
+      </c>
+      <c r="J83">
+        <v>-1</v>
+      </c>
+      <c r="K83">
+        <v>0.20563596994944311</v>
+      </c>
+      <c r="L83">
+        <v>0.998854725331347</v>
+      </c>
+      <c r="M83">
+        <v>0.2936529874477859</v>
+      </c>
+      <c r="N83">
+        <v>59.611823023939003</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B84">
+        <v>12</v>
+      </c>
+      <c r="C84">
+        <v>1771.0969814923101</v>
+      </c>
+      <c r="D84">
+        <v>1771.2612709215309</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>48.573040246963501</v>
+      </c>
+      <c r="G84">
+        <v>2</v>
+      </c>
+      <c r="H84">
+        <v>-1</v>
+      </c>
+      <c r="I84">
+        <v>-1</v>
+      </c>
+      <c r="J84">
+        <v>-1</v>
+      </c>
+      <c r="K84">
+        <v>0.21807794897487909</v>
+      </c>
+      <c r="L84">
+        <v>0.998920660783436</v>
+      </c>
+      <c r="M84">
+        <v>0.21844313874434201</v>
+      </c>
+      <c r="N84">
+        <v>59.55082429402075</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B85">
+        <v>13</v>
+      </c>
+      <c r="C85">
+        <v>1738.2229436649529</v>
+      </c>
+      <c r="D85">
+        <v>1738.393103471212</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>34.874751329421997</v>
+      </c>
+      <c r="G85">
+        <v>3</v>
+      </c>
+      <c r="H85">
+        <v>-1</v>
+      </c>
+      <c r="I85">
+        <v>-1</v>
+      </c>
+      <c r="J85">
+        <v>-1</v>
+      </c>
+      <c r="K85">
+        <v>0.24887979000881769</v>
+      </c>
+      <c r="L85">
+        <v>0.99933163839159145</v>
+      </c>
+      <c r="M85">
+        <v>0.26712263940066472</v>
+      </c>
+      <c r="N85">
+        <v>59.360410372623022</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86">
+        <v>14</v>
+      </c>
+      <c r="C86">
+        <v>1687.9356477671431</v>
+      </c>
+      <c r="D86">
+        <v>1688.0958104821359</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>40.589564323425293</v>
+      </c>
+      <c r="G86">
+        <v>4</v>
+      </c>
+      <c r="H86">
+        <v>-1</v>
+      </c>
+      <c r="I86">
+        <v>-1</v>
+      </c>
+      <c r="J86">
+        <v>-1</v>
+      </c>
+      <c r="K86">
+        <v>0.2195048988226492</v>
+      </c>
+      <c r="L86">
+        <v>0.99979405564217871</v>
+      </c>
+      <c r="M86">
+        <v>0.29748595837546282</v>
+      </c>
+      <c r="N86">
+        <v>59.385621165529372</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>19</v>
+      </c>
+      <c r="B87">
+        <v>15</v>
+      </c>
+      <c r="C87">
+        <v>1892.2262375892631</v>
+      </c>
+      <c r="D87">
+        <v>1892.4113972978851</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>71.595218896865845</v>
+      </c>
+      <c r="G87">
+        <v>3</v>
+      </c>
+      <c r="H87">
+        <v>-1</v>
+      </c>
+      <c r="I87">
+        <v>-1</v>
+      </c>
+      <c r="J87">
+        <v>-1</v>
+      </c>
+      <c r="K87">
+        <v>0.46537771250339849</v>
+      </c>
+      <c r="L87">
+        <v>0.99940891667962495</v>
+      </c>
+      <c r="M87">
+        <v>0.27352108693436439</v>
+      </c>
+      <c r="N87">
+        <v>58.785277353498337</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88">
+        <v>16</v>
+      </c>
+      <c r="C88">
+        <v>1762.1992644076331</v>
+      </c>
+      <c r="D88">
+        <v>1762.369407167635</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>44.29728364944458</v>
+      </c>
+      <c r="G88">
+        <v>3</v>
+      </c>
+      <c r="H88">
+        <v>-1</v>
+      </c>
+      <c r="I88">
+        <v>-1</v>
+      </c>
+      <c r="J88">
+        <v>-1</v>
+      </c>
+      <c r="K88">
+        <v>0.2340355353234406</v>
+      </c>
+      <c r="L88">
+        <v>0.99957702733801179</v>
+      </c>
+      <c r="M88">
+        <v>0.21627533287982131</v>
+      </c>
+      <c r="N88">
+        <v>59.35049284140571</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89">
+        <v>17</v>
+      </c>
+      <c r="C89">
+        <v>1789.1665105850641</v>
+      </c>
+      <c r="D89">
+        <v>1789.2939564044491</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>36.198395252227783</v>
+      </c>
+      <c r="G89">
+        <v>3</v>
+      </c>
+      <c r="H89">
+        <v>-1</v>
+      </c>
+      <c r="I89">
+        <v>-1</v>
+      </c>
+      <c r="J89">
+        <v>-1</v>
+      </c>
+      <c r="K89">
+        <v>0.22195339102532621</v>
+      </c>
+      <c r="L89">
+        <v>0.99872338532408655</v>
+      </c>
+      <c r="M89">
+        <v>0.25983205902079559</v>
+      </c>
+      <c r="N89">
+        <v>59.167713400682374</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>19</v>
+      </c>
+      <c r="B90">
+        <v>18</v>
+      </c>
+      <c r="C90">
+        <v>1774.6952094629801</v>
+      </c>
+      <c r="D90">
+        <v>1774.840109492869</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>76.680653810501099</v>
+      </c>
+      <c r="G90">
+        <v>2</v>
+      </c>
+      <c r="H90">
+        <v>-1</v>
+      </c>
+      <c r="I90">
+        <v>-1</v>
+      </c>
+      <c r="J90">
+        <v>-1</v>
+      </c>
+      <c r="K90">
+        <v>0.44753895244086062</v>
+      </c>
+      <c r="L90">
+        <v>0.99897045791479322</v>
+      </c>
+      <c r="M90">
+        <v>0.2977684335777836</v>
+      </c>
+      <c r="N90">
+        <v>59.319783974462588</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>19</v>
+      </c>
+      <c r="B91">
+        <v>19</v>
+      </c>
+      <c r="C91">
+        <v>1687.1631746753669</v>
+      </c>
+      <c r="D91">
+        <v>1687.3203247166271</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>41.132462024688721</v>
+      </c>
+      <c r="G91">
+        <v>2</v>
+      </c>
+      <c r="H91">
+        <v>-1</v>
+      </c>
+      <c r="I91">
+        <v>-1</v>
+      </c>
+      <c r="J91">
+        <v>-1</v>
+      </c>
+      <c r="K91">
+        <v>0.38141818397033828</v>
+      </c>
+      <c r="L91">
+        <v>0.99922746901452064</v>
+      </c>
+      <c r="M91">
+        <v>0.29479492184760581</v>
+      </c>
+      <c r="N91">
+        <v>59.540063737400899</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92">
+        <v>5</v>
+      </c>
+      <c r="C92">
+        <v>2103.940138394928</v>
+      </c>
+      <c r="D92">
+        <v>2104.129533716256</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>91.52849292755127</v>
+      </c>
+      <c r="H92">
+        <v>-1</v>
+      </c>
+      <c r="I92">
+        <v>-1</v>
+      </c>
+      <c r="J92">
+        <v>-1</v>
+      </c>
+      <c r="K92">
+        <v>0.35270164903352058</v>
+      </c>
+      <c r="L92">
+        <v>0.99969874374762224</v>
+      </c>
+      <c r="M92">
+        <v>0.28764273900474152</v>
+      </c>
+      <c r="N92">
+        <v>56.419473153529047</v>
+      </c>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>20</v>
+      </c>
+      <c r="B93">
+        <v>6</v>
+      </c>
+      <c r="C93">
+        <v>2065.1491496119638</v>
+      </c>
+      <c r="D93">
+        <v>2065.346641892846</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>180.78013443946841</v>
+      </c>
+      <c r="H93">
+        <v>-1</v>
+      </c>
+      <c r="I93">
+        <v>-1</v>
+      </c>
+      <c r="J93">
+        <v>-1</v>
+      </c>
+      <c r="K93">
+        <v>0.42010962340642471</v>
+      </c>
+      <c r="L93">
+        <v>0.99968447123229165</v>
+      </c>
+      <c r="M93">
+        <v>0.244598959814851</v>
+      </c>
+      <c r="N93">
+        <v>56.452557104070017</v>
+      </c>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94">
+        <v>7</v>
+      </c>
+      <c r="C94">
+        <v>2098.869534424085</v>
+      </c>
+      <c r="D94">
+        <v>2099.0645985898909</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>457.2009220123291</v>
+      </c>
+      <c r="H94">
+        <v>-1</v>
+      </c>
+      <c r="I94">
+        <v>-1</v>
+      </c>
+      <c r="J94">
+        <v>-1</v>
+      </c>
+      <c r="K94">
+        <v>0.66190275511030805</v>
+      </c>
+      <c r="L94">
+        <v>0.9991352105392195</v>
+      </c>
+      <c r="M94">
+        <v>0.29090647231490202</v>
+      </c>
+      <c r="N94">
+        <v>56.191180003752677</v>
+      </c>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>20</v>
+      </c>
+      <c r="B95">
+        <v>8</v>
+      </c>
+      <c r="C95">
+        <v>1922.336076503992</v>
+      </c>
+      <c r="D95">
+        <v>1922.496646860578</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>174.82924294471741</v>
+      </c>
+      <c r="H95">
+        <v>-1</v>
+      </c>
+      <c r="I95">
+        <v>-1</v>
+      </c>
+      <c r="J95">
+        <v>-1</v>
+      </c>
+      <c r="K95">
+        <v>0.3087473437112101</v>
+      </c>
+      <c r="L95">
+        <v>0.99936283227346134</v>
+      </c>
+      <c r="M95">
+        <v>0.34146813305678342</v>
+      </c>
+      <c r="N95">
+        <v>56.430305082698467</v>
+      </c>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>20</v>
+      </c>
+      <c r="B96">
+        <v>9</v>
+      </c>
+      <c r="C96">
+        <v>1983.0934161976329</v>
+      </c>
+      <c r="D96">
+        <v>1983.2313149474789</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>162.6695370674133</v>
+      </c>
+      <c r="H96">
+        <v>-1</v>
+      </c>
+      <c r="I96">
+        <v>-1</v>
+      </c>
+      <c r="J96">
+        <v>-1</v>
+      </c>
+      <c r="K96">
+        <v>0.26810034578552688</v>
+      </c>
+      <c r="L96">
+        <v>0.99895784160260193</v>
+      </c>
+      <c r="M96">
+        <v>0.28421188221467708</v>
+      </c>
+      <c r="N96">
+        <v>56.47651219412981</v>
+      </c>
+    </row>
+    <row r="97" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>20</v>
+      </c>
+      <c r="B97">
+        <v>10</v>
+      </c>
+      <c r="C97">
+        <v>2105.8210782673618</v>
+      </c>
+      <c r="D97">
+        <v>2106.026245734985</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>284.70235228538507</v>
+      </c>
+      <c r="H97">
+        <v>-1</v>
+      </c>
+      <c r="I97">
+        <v>-1</v>
+      </c>
+      <c r="J97">
+        <v>-1</v>
+      </c>
+      <c r="K97">
+        <v>0.42147126257861361</v>
+      </c>
+      <c r="L97">
+        <v>0.99932998869705181</v>
+      </c>
+      <c r="M97">
+        <v>0.27972309334447509</v>
+      </c>
+      <c r="N97">
+        <v>56.394659490363217</v>
+      </c>
+    </row>
+    <row r="98" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>20</v>
+      </c>
+      <c r="B98">
+        <v>11</v>
+      </c>
+      <c r="C98">
+        <v>2036.303123285353</v>
+      </c>
+      <c r="D98">
+        <v>2036.498859221826</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>184.69862651824951</v>
+      </c>
+      <c r="H98">
+        <v>-1</v>
+      </c>
+      <c r="I98">
+        <v>-1</v>
+      </c>
+      <c r="J98">
+        <v>-1</v>
+      </c>
+      <c r="K98">
+        <v>0.49022491063362772</v>
+      </c>
+      <c r="L98">
+        <v>0.9990551402883856</v>
+      </c>
+      <c r="M98">
+        <v>0.27973331854151312</v>
+      </c>
+      <c r="N98">
+        <v>56.353544696466287</v>
+      </c>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99">
+        <v>12</v>
+      </c>
+      <c r="C99">
+        <v>2095.5013337582459</v>
+      </c>
+      <c r="D99">
+        <v>2095.70424173831</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>221.3546431064606</v>
+      </c>
+      <c r="H99">
+        <v>-1</v>
+      </c>
+      <c r="I99">
+        <v>-1</v>
+      </c>
+      <c r="J99">
+        <v>-1</v>
+      </c>
+      <c r="K99">
+        <v>0.57381738489247203</v>
+      </c>
+      <c r="L99">
+        <v>0.99873522853012042</v>
+      </c>
+      <c r="M99">
+        <v>0.2229631329882423</v>
+      </c>
+      <c r="N99">
+        <v>56.365403947348803</v>
+      </c>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>20</v>
+      </c>
+      <c r="B100">
+        <v>13</v>
+      </c>
+      <c r="C100">
+        <v>2054.970802676914</v>
+      </c>
+      <c r="D100">
+        <v>2055.1520229655339</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>65.788003921508789</v>
+      </c>
+      <c r="H100">
+        <v>-1</v>
+      </c>
+      <c r="I100">
+        <v>-1</v>
+      </c>
+      <c r="J100">
+        <v>-1</v>
+      </c>
+      <c r="K100">
+        <v>0.36249919692406862</v>
+      </c>
+      <c r="L100">
+        <v>0.99963486332399398</v>
+      </c>
+      <c r="M100">
+        <v>0.26704911795879821</v>
+      </c>
+      <c r="N100">
+        <v>56.264780481664353</v>
+      </c>
+    </row>
+    <row r="101" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B101">
+        <v>14</v>
+      </c>
+      <c r="C101">
+        <v>1983.2148216705591</v>
+      </c>
+      <c r="D101">
+        <v>1983.4046233626491</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>62.953287601470947</v>
+      </c>
+      <c r="H101">
+        <v>-1</v>
+      </c>
+      <c r="I101">
+        <v>-1</v>
+      </c>
+      <c r="J101">
+        <v>-1</v>
+      </c>
+      <c r="K101">
+        <v>0.35545580294893792</v>
+      </c>
+      <c r="L101">
+        <v>0.99977571654694009</v>
+      </c>
+      <c r="M101">
+        <v>0.30151115467901912</v>
+      </c>
+      <c r="N101">
+        <v>56.44767552629871</v>
+      </c>
+    </row>
+    <row r="102" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>20</v>
+      </c>
+      <c r="B102">
+        <v>15</v>
+      </c>
+      <c r="C102">
+        <v>2247.453808587878</v>
+      </c>
+      <c r="D102">
+        <v>2247.541933496319</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>244.03174185752869</v>
+      </c>
+      <c r="H102">
+        <v>-1</v>
+      </c>
+      <c r="I102">
+        <v>-1</v>
+      </c>
+      <c r="J102">
+        <v>-1</v>
+      </c>
+      <c r="K102">
+        <v>0.55406131320699503</v>
+      </c>
+      <c r="L102">
+        <v>0.99987754491049563</v>
+      </c>
+      <c r="M102">
+        <v>0.26469596856123517</v>
+      </c>
+      <c r="N102">
+        <v>56.337623694250993</v>
+      </c>
+    </row>
+    <row r="103" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>20</v>
+      </c>
+      <c r="B103">
+        <v>16</v>
+      </c>
+      <c r="C103">
+        <v>2123.557460121543</v>
+      </c>
+      <c r="D103">
+        <v>2123.7440622390841</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>131.59731721878049</v>
+      </c>
+      <c r="H103">
+        <v>-1</v>
+      </c>
+      <c r="I103">
+        <v>-1</v>
+      </c>
+      <c r="J103">
+        <v>-1</v>
+      </c>
+      <c r="K103">
+        <v>0.53878953974295596</v>
+      </c>
+      <c r="L103">
+        <v>0.99982214583370277</v>
+      </c>
+      <c r="M103">
+        <v>0.22175848126230319</v>
+      </c>
+      <c r="N103">
+        <v>56.423129619577558</v>
+      </c>
+    </row>
+    <row r="104" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>20</v>
+      </c>
+      <c r="B104">
+        <v>17</v>
+      </c>
+      <c r="C104">
+        <v>2138.6450037590598</v>
+      </c>
+      <c r="D104">
+        <v>2138.8432306209438</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>218.4507329463959</v>
+      </c>
+      <c r="H104">
+        <v>-1</v>
+      </c>
+      <c r="I104">
+        <v>-1</v>
+      </c>
+      <c r="J104">
+        <v>-1</v>
+      </c>
+      <c r="K104">
+        <v>0.40247412334236432</v>
+      </c>
+      <c r="L104">
+        <v>0.99951859477222715</v>
+      </c>
+      <c r="M104">
+        <v>0.27360796677107108</v>
+      </c>
+      <c r="N104">
+        <v>56.261211321688307</v>
+      </c>
+    </row>
+    <row r="105" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>20</v>
+      </c>
+      <c r="B105">
+        <v>18</v>
+      </c>
+      <c r="C105">
+        <v>2146.664835181673</v>
+      </c>
+      <c r="D105">
+        <v>2146.8768169044042</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>241.07946872711179</v>
+      </c>
+      <c r="H105">
+        <v>-1</v>
+      </c>
+      <c r="I105">
+        <v>-1</v>
+      </c>
+      <c r="J105">
+        <v>-1</v>
+      </c>
+      <c r="K105">
+        <v>0.547757179684636</v>
+      </c>
+      <c r="L105">
+        <v>0.99955137950420414</v>
+      </c>
+      <c r="M105">
+        <v>0.28159240131938251</v>
+      </c>
+      <c r="N105">
+        <v>56.509496570267338</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>20</v>
+      </c>
+      <c r="B106">
+        <v>19</v>
+      </c>
+      <c r="C106">
+        <v>1958.2391976816091</v>
+      </c>
+      <c r="D106">
+        <v>1958.4269538919971</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>83.507676362991333</v>
+      </c>
+      <c r="H106">
+        <v>-1</v>
+      </c>
+      <c r="I106">
+        <v>-1</v>
+      </c>
+      <c r="J106">
+        <v>-1</v>
+      </c>
+      <c r="K106">
+        <v>0.49604498013024978</v>
+      </c>
+      <c r="L106">
+        <v>0.99954283361995899</v>
+      </c>
+      <c r="M106">
+        <v>0.29841032252557842</v>
+      </c>
+      <c r="N106">
+        <v>56.475435464056282</v>
       </c>
     </row>
   </sheetData>
